--- a/grupos/4ALCV - Estadisticos 20232.xlsx
+++ b/grupos/4ALCV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="84">
   <si>
     <t>Materia</t>
   </si>
@@ -188,24 +188,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
     <t>Valerio González Valeria</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
+    <t>González Nuñez Veronica</t>
   </si>
   <si>
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
+    <t>Urias Morales Alejandra</t>
+  </si>
+  <si>
     <t>Reyes Cruz Eder Yaveth</t>
   </si>
   <si>
-    <t>Urias Morales Alejandra</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -218,31 +218,16 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
-    <t>ESCOBAR</t>
-  </si>
-  <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>GAYTAN</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
+    <t>DE ROMAN</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>TEPOLE</t>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
   </si>
   <si>
     <t>VALENTE</t>
@@ -251,28 +236,16 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>GROT</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
+    <t>CORTES</t>
   </si>
   <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>TETLACTLE</t>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>PULIDO</t>
@@ -281,31 +254,16 @@
     <t>TZOMPAXTLE</t>
   </si>
   <si>
-    <t>KEVIN ALEXIS</t>
-  </si>
-  <si>
-    <t>LUZ ALONDRA</t>
-  </si>
-  <si>
-    <t>ANA SHECIT</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ATZIN LUCERO</t>
-  </si>
-  <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>ADAMARI</t>
+    <t>NATHALI</t>
   </si>
   <si>
     <t>KAREN</t>
   </si>
   <si>
-    <t>JONATHAN</t>
+    <t>AZURA</t>
+  </si>
+  <si>
+    <t>NOEMI DEL ROCIO</t>
   </si>
   <si>
     <t>JUAN EMANUEL</t>
@@ -838,25 +796,25 @@
         <v>7</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -889,16 +847,16 @@
         <v>6</v>
       </c>
       <c r="Z4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB4">
         <v>9</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -927,25 +885,25 @@
         <v>8</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -975,19 +933,19 @@
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC5">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1016,25 +974,25 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1067,16 +1025,16 @@
         <v>9</v>
       </c>
       <c r="Z6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1105,25 +1063,25 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1165,7 +1123,7 @@
         <v>7</v>
       </c>
       <c r="AC7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1194,25 +1152,25 @@
         <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1242,16 +1200,16 @@
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z8">
         <v>9</v>
       </c>
       <c r="AA8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC8">
         <v>9</v>
@@ -1283,25 +1241,25 @@
         <v>7</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1331,16 +1289,16 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z9">
         <v>5</v>
       </c>
       <c r="AA9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC9">
         <v>7</v>
@@ -1372,25 +1330,25 @@
         <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1414,25 +1372,25 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1461,25 +1419,25 @@
         <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1506,10 +1464,10 @@
         <v>5</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z11">
         <v>8</v>
@@ -1521,7 +1479,7 @@
         <v>6</v>
       </c>
       <c r="AC11">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1550,25 +1508,25 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1595,22 +1553,22 @@
         <v>5</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>5</v>
       </c>
       <c r="Z12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA12">
         <v>7</v>
       </c>
       <c r="AB12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC12">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1639,25 +1597,25 @@
         <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1687,19 +1645,19 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z13">
         <v>8</v>
       </c>
       <c r="AA13">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC13">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1728,25 +1686,25 @@
         <v>5</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1773,13 +1731,13 @@
         <v>5</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y14">
         <v>5</v>
       </c>
       <c r="Z14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA14">
         <v>5</v>
@@ -1788,7 +1746,7 @@
         <v>5</v>
       </c>
       <c r="AC14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1817,25 +1775,25 @@
         <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1859,19 +1817,19 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z15">
         <v>8</v>
       </c>
       <c r="AA15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB15">
         <v>9</v>
@@ -1906,25 +1864,25 @@
         <v>4</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1954,7 +1912,7 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z16">
         <v>5</v>
@@ -1963,7 +1921,7 @@
         <v>5</v>
       </c>
       <c r="AB16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC16">
         <v>5</v>
@@ -1995,25 +1953,25 @@
         <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2043,13 +2001,13 @@
         <v>10</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z17">
         <v>10</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB17">
         <v>9</v>
@@ -2084,25 +2042,25 @@
         <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2135,16 +2093,16 @@
         <v>9</v>
       </c>
       <c r="Z18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA18">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB18">
         <v>9</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2173,25 +2131,25 @@
         <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2227,10 +2185,10 @@
         <v>5</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC19">
         <v>6</v>
@@ -2262,25 +2220,25 @@
         <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2316,10 +2274,10 @@
         <v>10</v>
       </c>
       <c r="AA20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC20">
         <v>9</v>
@@ -2351,25 +2309,25 @@
         <v>5</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2396,22 +2354,22 @@
         <v>5</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z21">
         <v>5</v>
       </c>
       <c r="AA21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC21">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2440,25 +2398,25 @@
         <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2482,16 +2440,16 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA22">
         <v>7</v>
@@ -2529,25 +2487,25 @@
         <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2577,16 +2535,16 @@
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z23">
         <v>9</v>
       </c>
       <c r="AA23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC23">
         <v>9</v>
@@ -2618,25 +2576,25 @@
         <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2666,19 +2624,19 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z24">
         <v>10</v>
       </c>
       <c r="AA24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2707,25 +2665,25 @@
         <v>8</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2749,25 +2707,25 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z25">
         <v>8</v>
       </c>
       <c r="AA25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC25">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2796,25 +2754,25 @@
         <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2885,25 +2843,25 @@
         <v>5</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2933,19 +2891,19 @@
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA27">
         <v>6</v>
       </c>
       <c r="AB27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC27">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2974,25 +2932,25 @@
         <v>5</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3019,7 +2977,7 @@
         <v>5</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y28">
         <v>5</v>
@@ -3028,13 +2986,13 @@
         <v>6</v>
       </c>
       <c r="AA28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC28">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3063,25 +3021,25 @@
         <v>5</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3152,25 +3110,25 @@
         <v>9</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3206,10 +3164,10 @@
         <v>10</v>
       </c>
       <c r="AA30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC30">
         <v>9</v>
@@ -3241,25 +3199,25 @@
         <v>7</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3289,19 +3247,19 @@
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z31">
         <v>9</v>
       </c>
       <c r="AA31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC31">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3330,25 +3288,25 @@
         <v>7</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3375,22 +3333,22 @@
         <v>9</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y32">
         <v>5</v>
       </c>
       <c r="Z32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC32">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3419,25 +3377,25 @@
         <v>8</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3467,19 +3425,19 @@
         <v>9</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC33">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3508,25 +3466,25 @@
         <v>8</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3550,22 +3508,22 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X34">
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z34">
         <v>8</v>
       </c>
       <c r="AA34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC34">
         <v>8</v>
@@ -3719,13 +3677,13 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="J4">
-        <v>85</v>
+        <v>89.2</v>
       </c>
       <c r="K4">
-        <v>92</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="L4">
         <v>100</v>
@@ -3740,13 +3698,13 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q4">
-        <v>85</v>
+        <v>89.2</v>
       </c>
       <c r="R4">
-        <v>92</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -3787,13 +3745,13 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="J5">
         <v>100</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="L5">
         <v>100</v>
@@ -3808,13 +3766,13 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="Q5">
         <v>100</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -3855,13 +3813,13 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="J6">
         <v>100</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -3876,13 +3834,13 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="Q6">
         <v>100</v>
       </c>
       <c r="R6">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -3923,46 +3881,46 @@
         <v>83.3</v>
       </c>
       <c r="I7">
-        <v>91.7</v>
+        <v>93.5</v>
       </c>
       <c r="J7">
+        <v>83.8</v>
+      </c>
+      <c r="K7">
+        <v>91.5</v>
+      </c>
+      <c r="L7">
+        <v>100</v>
+      </c>
+      <c r="M7">
+        <v>100</v>
+      </c>
+      <c r="N7">
+        <v>100</v>
+      </c>
+      <c r="O7">
         <v>85</v>
       </c>
-      <c r="K7">
-        <v>92</v>
-      </c>
-      <c r="L7">
-        <v>100</v>
-      </c>
-      <c r="M7">
-        <v>100</v>
-      </c>
-      <c r="N7">
-        <v>100</v>
-      </c>
-      <c r="O7">
-        <v>83.3</v>
-      </c>
       <c r="P7">
-        <v>91.7</v>
+        <v>93.5</v>
       </c>
       <c r="Q7">
+        <v>83.8</v>
+      </c>
+      <c r="R7">
+        <v>91.5</v>
+      </c>
+      <c r="S7">
+        <v>100</v>
+      </c>
+      <c r="T7">
+        <v>100</v>
+      </c>
+      <c r="U7">
+        <v>100</v>
+      </c>
+      <c r="V7">
         <v>85</v>
-      </c>
-      <c r="R7">
-        <v>92</v>
-      </c>
-      <c r="S7">
-        <v>100</v>
-      </c>
-      <c r="T7">
-        <v>100</v>
-      </c>
-      <c r="U7">
-        <v>100</v>
-      </c>
-      <c r="V7">
-        <v>83.3</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -3991,7 +3949,7 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="J8">
         <v>100</v>
@@ -4012,7 +3970,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -4059,46 +4017,46 @@
         <v>100</v>
       </c>
       <c r="I9">
+        <v>93.5</v>
+      </c>
+      <c r="J9">
+        <v>86.5</v>
+      </c>
+      <c r="K9">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="L9">
+        <v>100</v>
+      </c>
+      <c r="M9">
+        <v>100</v>
+      </c>
+      <c r="N9">
+        <v>100</v>
+      </c>
+      <c r="O9">
         <v>91.7</v>
       </c>
-      <c r="J9">
-        <v>85</v>
-      </c>
-      <c r="K9">
-        <v>92</v>
-      </c>
-      <c r="L9">
-        <v>100</v>
-      </c>
-      <c r="M9">
-        <v>100</v>
-      </c>
-      <c r="N9">
-        <v>100</v>
-      </c>
-      <c r="O9">
-        <v>100</v>
-      </c>
       <c r="P9">
+        <v>93.5</v>
+      </c>
+      <c r="Q9">
+        <v>86.5</v>
+      </c>
+      <c r="R9">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="S9">
+        <v>100</v>
+      </c>
+      <c r="T9">
+        <v>100</v>
+      </c>
+      <c r="U9">
+        <v>100</v>
+      </c>
+      <c r="V9">
         <v>91.7</v>
-      </c>
-      <c r="Q9">
-        <v>85</v>
-      </c>
-      <c r="R9">
-        <v>92</v>
-      </c>
-      <c r="S9">
-        <v>100</v>
-      </c>
-      <c r="T9">
-        <v>100</v>
-      </c>
-      <c r="U9">
-        <v>100</v>
-      </c>
-      <c r="V9">
-        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4130,10 +4088,10 @@
         <v>100</v>
       </c>
       <c r="J10">
-        <v>90</v>
+        <v>86.5</v>
       </c>
       <c r="K10">
-        <v>96</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -4151,10 +4109,10 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>90</v>
+        <v>86.5</v>
       </c>
       <c r="R10">
-        <v>96</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -4195,46 +4153,46 @@
         <v>100</v>
       </c>
       <c r="I11">
+        <v>95.7</v>
+      </c>
+      <c r="J11">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="K11">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="L11">
+        <v>100</v>
+      </c>
+      <c r="M11">
+        <v>100</v>
+      </c>
+      <c r="N11">
+        <v>100</v>
+      </c>
+      <c r="O11">
         <v>91.7</v>
       </c>
-      <c r="J11">
-        <v>85</v>
-      </c>
-      <c r="K11">
-        <v>100</v>
-      </c>
-      <c r="L11">
-        <v>100</v>
-      </c>
-      <c r="M11">
-        <v>100</v>
-      </c>
-      <c r="N11">
-        <v>100</v>
-      </c>
-      <c r="O11">
-        <v>100</v>
-      </c>
       <c r="P11">
+        <v>95.7</v>
+      </c>
+      <c r="Q11">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="R11">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="S11">
+        <v>100</v>
+      </c>
+      <c r="T11">
+        <v>100</v>
+      </c>
+      <c r="U11">
+        <v>100</v>
+      </c>
+      <c r="V11">
         <v>91.7</v>
-      </c>
-      <c r="Q11">
-        <v>85</v>
-      </c>
-      <c r="R11">
-        <v>100</v>
-      </c>
-      <c r="S11">
-        <v>100</v>
-      </c>
-      <c r="T11">
-        <v>100</v>
-      </c>
-      <c r="U11">
-        <v>100</v>
-      </c>
-      <c r="V11">
-        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -4263,13 +4221,13 @@
         <v>66.7</v>
       </c>
       <c r="I12">
-        <v>91.7</v>
+        <v>93.5</v>
       </c>
       <c r="J12">
-        <v>85</v>
+        <v>83.8</v>
       </c>
       <c r="K12">
-        <v>68</v>
+        <v>61.7</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -4281,16 +4239,16 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>66.7</v>
+        <v>63.3</v>
       </c>
       <c r="P12">
-        <v>91.7</v>
+        <v>93.5</v>
       </c>
       <c r="Q12">
-        <v>85</v>
+        <v>83.8</v>
       </c>
       <c r="R12">
-        <v>68</v>
+        <v>61.7</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -4302,7 +4260,7 @@
         <v>100</v>
       </c>
       <c r="V12">
-        <v>66.7</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -4331,13 +4289,13 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="J13">
-        <v>90</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="K13">
-        <v>92</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -4352,13 +4310,13 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q13">
-        <v>90</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R13">
-        <v>92</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -4399,13 +4357,13 @@
         <v>50</v>
       </c>
       <c r="I14">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="J14">
-        <v>85</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="K14">
-        <v>92</v>
+        <v>91.5</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -4417,16 +4375,16 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="P14">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="Q14">
-        <v>85</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="R14">
-        <v>92</v>
+        <v>91.5</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -4438,7 +4396,7 @@
         <v>100</v>
       </c>
       <c r="V14">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -4467,13 +4425,13 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="J15">
-        <v>90</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="L15">
         <v>100</v>
@@ -4488,13 +4446,13 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q15">
-        <v>90</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R15">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -4535,13 +4493,13 @@
         <v>50</v>
       </c>
       <c r="I16">
-        <v>91.7</v>
+        <v>93.5</v>
       </c>
       <c r="J16">
-        <v>85</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="K16">
-        <v>80</v>
+        <v>78.7</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -4553,16 +4511,16 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="P16">
-        <v>91.7</v>
+        <v>93.5</v>
       </c>
       <c r="Q16">
-        <v>85</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="R16">
-        <v>80</v>
+        <v>78.7</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -4574,7 +4532,7 @@
         <v>100</v>
       </c>
       <c r="V16">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -4603,13 +4561,13 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="J17">
         <v>100</v>
       </c>
       <c r="K17">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -4624,13 +4582,13 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="Q17">
         <v>100</v>
       </c>
       <c r="R17">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -4671,13 +4629,13 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="J18">
         <v>100</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -4692,13 +4650,13 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="Q18">
         <v>100</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -4739,13 +4697,13 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>91.7</v>
+        <v>93.5</v>
       </c>
       <c r="J19">
-        <v>85</v>
+        <v>86.5</v>
       </c>
       <c r="K19">
-        <v>92</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -4760,13 +4718,13 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>91.7</v>
+        <v>93.5</v>
       </c>
       <c r="Q19">
-        <v>85</v>
+        <v>86.5</v>
       </c>
       <c r="R19">
-        <v>92</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -4807,7 +4765,7 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="J20">
         <v>100</v>
@@ -4828,7 +4786,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -4875,13 +4833,13 @@
         <v>83.3</v>
       </c>
       <c r="I21">
-        <v>91.7</v>
+        <v>93.5</v>
       </c>
       <c r="J21">
-        <v>85</v>
+        <v>83.8</v>
       </c>
       <c r="K21">
-        <v>92</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -4896,13 +4854,13 @@
         <v>83.3</v>
       </c>
       <c r="P21">
-        <v>91.7</v>
+        <v>93.5</v>
       </c>
       <c r="Q21">
-        <v>85</v>
+        <v>83.8</v>
       </c>
       <c r="R21">
-        <v>92</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -4943,10 +4901,10 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>91.7</v>
+        <v>95.7</v>
       </c>
       <c r="J22">
-        <v>90</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="K22">
         <v>100</v>
@@ -4964,10 +4922,10 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>91.7</v>
+        <v>95.7</v>
       </c>
       <c r="Q22">
-        <v>90</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -5011,7 +4969,7 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="J23">
         <v>100</v>
@@ -5032,7 +4990,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -5079,13 +5037,13 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="J24">
         <v>100</v>
       </c>
       <c r="K24">
-        <v>100</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -5100,13 +5058,13 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="Q24">
         <v>100</v>
       </c>
       <c r="R24">
-        <v>100</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -5147,13 +5105,13 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="J25">
-        <v>95</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="L25">
         <v>100</v>
@@ -5168,13 +5126,13 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="Q25">
-        <v>95</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R25">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -5215,16 +5173,16 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>91.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="J26">
-        <v>85</v>
+        <v>83.8</v>
       </c>
       <c r="K26">
-        <v>92</v>
+        <v>74.5</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M26">
         <v>100</v>
@@ -5233,19 +5191,19 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="P26">
-        <v>91.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="Q26">
-        <v>85</v>
+        <v>83.8</v>
       </c>
       <c r="R26">
-        <v>92</v>
+        <v>74.5</v>
       </c>
       <c r="S26">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T26">
         <v>100</v>
@@ -5254,7 +5212,7 @@
         <v>100</v>
       </c>
       <c r="V26">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -5283,13 +5241,13 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>91.7</v>
+        <v>95.7</v>
       </c>
       <c r="J27">
-        <v>90</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -5304,13 +5262,13 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>91.7</v>
+        <v>95.7</v>
       </c>
       <c r="Q27">
-        <v>90</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R27">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -5351,13 +5309,13 @@
         <v>50</v>
       </c>
       <c r="I28">
-        <v>91.7</v>
+        <v>93.5</v>
       </c>
       <c r="J28">
-        <v>85</v>
+        <v>83.8</v>
       </c>
       <c r="K28">
-        <v>72</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -5369,16 +5327,16 @@
         <v>100</v>
       </c>
       <c r="O28">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="P28">
-        <v>91.7</v>
+        <v>93.5</v>
       </c>
       <c r="Q28">
-        <v>85</v>
+        <v>83.8</v>
       </c>
       <c r="R28">
-        <v>72</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -5390,7 +5348,7 @@
         <v>100</v>
       </c>
       <c r="V28">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -5419,16 +5377,16 @@
         <v>83.3</v>
       </c>
       <c r="I29">
-        <v>91.7</v>
+        <v>93.5</v>
       </c>
       <c r="J29">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="K29">
-        <v>92</v>
+        <v>87.2</v>
       </c>
       <c r="L29">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="M29">
         <v>100</v>
@@ -5437,19 +5395,19 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="P29">
-        <v>91.7</v>
+        <v>93.5</v>
       </c>
       <c r="Q29">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="R29">
-        <v>92</v>
+        <v>87.2</v>
       </c>
       <c r="S29">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="T29">
         <v>100</v>
@@ -5458,7 +5416,7 @@
         <v>100</v>
       </c>
       <c r="V29">
-        <v>83.3</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -5487,13 +5445,13 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="J30">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="K30">
-        <v>100</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="L30">
         <v>100</v>
@@ -5508,13 +5466,13 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="Q30">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="R30">
-        <v>100</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -5555,13 +5513,13 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="J31">
         <v>100</v>
       </c>
       <c r="K31">
-        <v>92</v>
+        <v>91.5</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -5576,13 +5534,13 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="Q31">
         <v>100</v>
       </c>
       <c r="R31">
-        <v>92</v>
+        <v>91.5</v>
       </c>
       <c r="S31">
         <v>100</v>
@@ -5623,13 +5581,13 @@
         <v>100</v>
       </c>
       <c r="I32">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="J32">
-        <v>85</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="K32">
-        <v>92</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="L32">
         <v>100</v>
@@ -5644,13 +5602,13 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="Q32">
-        <v>85</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="R32">
-        <v>92</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="S32">
         <v>100</v>
@@ -5691,13 +5649,13 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="J33">
-        <v>85</v>
+        <v>86.5</v>
       </c>
       <c r="K33">
-        <v>92</v>
+        <v>95.7</v>
       </c>
       <c r="L33">
         <v>100</v>
@@ -5712,13 +5670,13 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q33">
-        <v>85</v>
+        <v>86.5</v>
       </c>
       <c r="R33">
-        <v>92</v>
+        <v>95.7</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -5759,13 +5717,13 @@
         <v>100</v>
       </c>
       <c r="I34">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="J34">
-        <v>90</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="K34">
-        <v>8</v>
+        <v>48.9</v>
       </c>
       <c r="L34">
         <v>100</v>
@@ -5780,13 +5738,13 @@
         <v>100</v>
       </c>
       <c r="P34">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q34">
-        <v>90</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R34">
-        <v>8</v>
+        <v>48.9</v>
       </c>
       <c r="S34">
         <v>100</v>
@@ -5855,7 +5813,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
@@ -5864,19 +5822,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>41.9</v>
+        <v>54.8</v>
       </c>
       <c r="G2" s="2">
-        <v>58.1</v>
+        <v>45.2</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5887,7 +5845,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -5896,19 +5854,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2">
-        <v>58.1</v>
+        <v>71</v>
       </c>
       <c r="G3" s="2">
-        <v>41.9</v>
+        <v>29</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5919,7 +5877,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -5928,19 +5886,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="2">
-        <v>74.2</v>
+        <v>71</v>
       </c>
       <c r="G4" s="2">
-        <v>25.8</v>
+        <v>29</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5951,7 +5909,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -5960,19 +5918,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="2">
-        <v>74.2</v>
+        <v>71</v>
       </c>
       <c r="G5" s="2">
-        <v>25.8</v>
+        <v>29</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6004,7 +5962,7 @@
         <v>19.4</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6015,10 +5973,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C7">
         <v>31</v>
@@ -6047,28 +6005,28 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C8">
         <v>31</v>
       </c>
       <c r="D8">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2">
-        <v>80.59999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="G8" s="2">
-        <v>19.4</v>
+        <v>12.9</v>
       </c>
       <c r="H8">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6118,7 +6076,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6150,22 +6108,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920236</v>
+        <v>22330051920235</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6173,22 +6131,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920236</v>
+        <v>22330051920235</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6196,22 +6154,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920237</v>
+        <v>22330051920257</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6219,19 +6177,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920237</v>
+        <v>22330051920257</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
         <v>58</v>
@@ -6242,22 +6200,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920234</v>
+        <v>22330051920230</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6265,19 +6223,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920241</v>
+        <v>22330051920253</v>
       </c>
       <c r="B7" t="s">
         <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
         <v>56</v>
@@ -6288,19 +6246,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920250</v>
+        <v>22330051920401</v>
       </c>
       <c r="B8" t="s">
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
         <v>56</v>
@@ -6311,139 +6269,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920251</v>
+        <v>22330051920259</v>
       </c>
       <c r="B9" t="s">
         <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
         <v>56</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920375</v>
-      </c>
-      <c r="B10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920257</v>
-      </c>
-      <c r="B11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" t="s">
-        <v>94</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920256</v>
-      </c>
-      <c r="B12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920401</v>
-      </c>
-      <c r="B13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" t="s">
-        <v>96</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920259</v>
-      </c>
-      <c r="B14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" t="s">
-        <v>97</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ALCV - Estadisticos 20232.xlsx
+++ b/grupos/4ALCV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="81">
   <si>
     <t>Materia</t>
   </si>
@@ -188,24 +188,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Rivera Serra Alma Lilian</t>
+  </si>
+  <si>
+    <t>Valerio González Valeria</t>
+  </si>
+  <si>
+    <t>Reyes Cruz Eder Yaveth</t>
+  </si>
+  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
-    <t>Valerio González Valeria</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Rivera Serra Alma Lilian</t>
-  </si>
-  <si>
     <t>Urias Morales Alejandra</t>
   </si>
   <si>
-    <t>Reyes Cruz Eder Yaveth</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -218,55 +218,46 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
     <t>DE ROMAN</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
     <t>ANGELES</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
     <t>CORTES</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>ROCHA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>PULIDO</t>
-  </si>
-  <si>
     <t>TZOMPAXTLE</t>
   </si>
   <si>
+    <t>ALDO EMANUEL</t>
+  </si>
+  <si>
+    <t>FERNANDA MARGARITA</t>
+  </si>
+  <si>
     <t>NATHALI</t>
   </si>
   <si>
-    <t>KAREN</t>
-  </si>
-  <si>
     <t>AZURA</t>
-  </si>
-  <si>
-    <t>NOEMI DEL ROCIO</t>
-  </si>
-  <si>
-    <t>JUAN EMANUEL</t>
   </si>
   <si>
     <t>BRENDA JANELY</t>
@@ -817,16 +808,16 @@
         <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
         <v>-1</v>
@@ -835,16 +826,16 @@
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>8</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z4">
         <v>5</v>
@@ -906,16 +897,16 @@
         <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>-1</v>
@@ -924,7 +915,7 @@
         <v>-1</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -995,16 +986,16 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>-1</v>
@@ -1013,7 +1004,7 @@
         <v>-1</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1084,16 +1075,16 @@
         <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <v>-1</v>
@@ -1102,19 +1093,19 @@
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA7">
         <v>5</v>
@@ -1123,7 +1114,7 @@
         <v>7</v>
       </c>
       <c r="AC7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1173,16 +1164,16 @@
         <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
         <v>-1</v>
@@ -1191,7 +1182,7 @@
         <v>-1</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>8</v>
@@ -1203,7 +1194,7 @@
         <v>8</v>
       </c>
       <c r="Z8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA8">
         <v>9</v>
@@ -1262,16 +1253,16 @@
         <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>-1</v>
@@ -1280,16 +1271,16 @@
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z9">
         <v>5</v>
@@ -1351,16 +1342,16 @@
         <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
         <v>-1</v>
@@ -1369,7 +1360,7 @@
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -1381,7 +1372,7 @@
         <v>7</v>
       </c>
       <c r="Z10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA10">
         <v>8</v>
@@ -1431,25 +1422,25 @@
         <v>7</v>
       </c>
       <c r="M11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O11">
         <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T11">
         <v>-1</v>
@@ -1458,28 +1449,28 @@
         <v>-1</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>7</v>
       </c>
       <c r="Z11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA11">
         <v>5</v>
       </c>
       <c r="AB11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1529,16 +1520,16 @@
         <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T12">
         <v>-1</v>
@@ -1547,10 +1538,10 @@
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>6</v>
@@ -1618,16 +1609,16 @@
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
         <v>-1</v>
@@ -1636,19 +1627,19 @@
         <v>-1</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>6</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>7</v>
       </c>
       <c r="Z13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA13">
         <v>8</v>
@@ -1707,16 +1698,16 @@
         <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
         <v>-1</v>
@@ -1725,10 +1716,10 @@
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>5</v>
@@ -1746,7 +1737,7 @@
         <v>5</v>
       </c>
       <c r="AC14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1796,16 +1787,16 @@
         <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
         <v>-1</v>
@@ -1814,7 +1805,7 @@
         <v>-1</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1826,7 +1817,7 @@
         <v>7</v>
       </c>
       <c r="Z15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA15">
         <v>7</v>
@@ -1885,16 +1876,16 @@
         <v>7</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>-1</v>
@@ -1903,16 +1894,16 @@
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z16">
         <v>5</v>
@@ -1974,16 +1965,16 @@
         <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>-1</v>
@@ -1992,7 +1983,7 @@
         <v>-1</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -2001,10 +1992,10 @@
         <v>10</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA17">
         <v>9</v>
@@ -2057,22 +2048,22 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O18">
         <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>-1</v>
@@ -2081,7 +2072,7 @@
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -2093,7 +2084,7 @@
         <v>9</v>
       </c>
       <c r="Z18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <v>9</v>
@@ -2152,16 +2143,16 @@
         <v>6</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
         <v>-1</v>
@@ -2170,13 +2161,13 @@
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -2191,7 +2182,7 @@
         <v>5</v>
       </c>
       <c r="AC19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2241,16 +2232,16 @@
         <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>-1</v>
@@ -2259,7 +2250,7 @@
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>9</v>
@@ -2268,10 +2259,10 @@
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA20">
         <v>9</v>
@@ -2330,16 +2321,16 @@
         <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
         <v>-1</v>
@@ -2348,7 +2339,7 @@
         <v>-1</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>5</v>
@@ -2369,7 +2360,7 @@
         <v>6</v>
       </c>
       <c r="AC21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2419,16 +2410,16 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
         <v>-1</v>
@@ -2437,19 +2428,19 @@
         <v>-1</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA22">
         <v>7</v>
@@ -2499,7 +2490,7 @@
         <v>9</v>
       </c>
       <c r="M23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>9</v>
@@ -2508,16 +2499,16 @@
         <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
         <v>-1</v>
@@ -2526,7 +2517,7 @@
         <v>-1</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>7</v>
@@ -2538,10 +2529,10 @@
         <v>7</v>
       </c>
       <c r="Z23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>8</v>
@@ -2597,16 +2588,16 @@
         <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
         <v>-1</v>
@@ -2615,19 +2606,19 @@
         <v>-1</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>7</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>7</v>
       </c>
       <c r="Z24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA24">
         <v>8</v>
@@ -2686,16 +2677,16 @@
         <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
         <v>-1</v>
@@ -2704,7 +2695,7 @@
         <v>-1</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>8</v>
@@ -2713,10 +2704,10 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA25">
         <v>9</v>
@@ -2775,16 +2766,16 @@
         <v>5</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T26">
         <v>-1</v>
@@ -2793,7 +2784,7 @@
         <v>-1</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W26">
         <v>5</v>
@@ -2864,16 +2855,16 @@
         <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T27">
         <v>-1</v>
@@ -2882,19 +2873,19 @@
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>7</v>
       </c>
       <c r="Z27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA27">
         <v>6</v>
@@ -2903,7 +2894,7 @@
         <v>7</v>
       </c>
       <c r="AC27">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2953,16 +2944,16 @@
         <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T28">
         <v>-1</v>
@@ -2971,7 +2962,7 @@
         <v>-1</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W28">
         <v>5</v>
@@ -2983,7 +2974,7 @@
         <v>5</v>
       </c>
       <c r="Z28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA28">
         <v>5</v>
@@ -2992,7 +2983,7 @@
         <v>7</v>
       </c>
       <c r="AC28">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3042,16 +3033,16 @@
         <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T29">
         <v>-1</v>
@@ -3060,10 +3051,10 @@
         <v>-1</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>5</v>
@@ -3125,22 +3116,22 @@
         <v>9</v>
       </c>
       <c r="N30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O30">
         <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T30">
         <v>-1</v>
@@ -3149,7 +3140,7 @@
         <v>-1</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3161,13 +3152,13 @@
         <v>7</v>
       </c>
       <c r="Z30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA30">
         <v>9</v>
       </c>
       <c r="AB30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC30">
         <v>9</v>
@@ -3220,16 +3211,16 @@
         <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T31">
         <v>-1</v>
@@ -3238,19 +3229,19 @@
         <v>-1</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA31">
         <v>8</v>
@@ -3300,7 +3291,7 @@
         <v>5</v>
       </c>
       <c r="M32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N32">
         <v>9</v>
@@ -3309,16 +3300,16 @@
         <v>8</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
         <v>-1</v>
@@ -3327,19 +3318,19 @@
         <v>-1</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>9</v>
       </c>
       <c r="X32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA32">
         <v>7</v>
@@ -3398,16 +3389,16 @@
         <v>6</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
         <v>-1</v>
@@ -3416,10 +3407,10 @@
         <v>-1</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X33">
         <v>9</v>
@@ -3428,7 +3419,7 @@
         <v>8</v>
       </c>
       <c r="Z33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA33">
         <v>8</v>
@@ -3487,16 +3478,16 @@
         <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T34">
         <v>-1</v>
@@ -3505,19 +3496,19 @@
         <v>-1</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA34">
         <v>8</v>
@@ -3526,7 +3517,7 @@
         <v>8</v>
       </c>
       <c r="AC34">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3698,13 +3689,13 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q4">
-        <v>89.2</v>
+        <v>92</v>
       </c>
       <c r="R4">
-        <v>85.09999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -3716,7 +3707,7 @@
         <v>100</v>
       </c>
       <c r="V4">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3772,7 +3763,7 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>97.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -3840,7 +3831,7 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>97.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -3902,13 +3893,13 @@
         <v>85</v>
       </c>
       <c r="P7">
-        <v>93.5</v>
+        <v>95.5</v>
       </c>
       <c r="Q7">
-        <v>83.8</v>
+        <v>84</v>
       </c>
       <c r="R7">
-        <v>91.5</v>
+        <v>94.2</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -3920,7 +3911,7 @@
         <v>100</v>
       </c>
       <c r="V7">
-        <v>85</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -4038,13 +4029,13 @@
         <v>91.7</v>
       </c>
       <c r="P9">
-        <v>93.5</v>
+        <v>95.5</v>
       </c>
       <c r="Q9">
-        <v>86.5</v>
+        <v>86</v>
       </c>
       <c r="R9">
-        <v>85.09999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -4056,7 +4047,7 @@
         <v>100</v>
       </c>
       <c r="V9">
-        <v>91.7</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4109,10 +4100,10 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>86.5</v>
+        <v>88</v>
       </c>
       <c r="R10">
-        <v>97.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -4174,16 +4165,16 @@
         <v>91.7</v>
       </c>
       <c r="P11">
+        <v>95.5</v>
+      </c>
+      <c r="Q11">
+        <v>90</v>
+      </c>
+      <c r="R11">
         <v>95.7</v>
       </c>
-      <c r="Q11">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="R11">
-        <v>97.90000000000001</v>
-      </c>
       <c r="S11">
-        <v>100</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="T11">
         <v>100</v>
@@ -4192,7 +4183,7 @@
         <v>100</v>
       </c>
       <c r="V11">
-        <v>91.7</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -4242,16 +4233,16 @@
         <v>63.3</v>
       </c>
       <c r="P12">
-        <v>93.5</v>
+        <v>95.5</v>
       </c>
       <c r="Q12">
-        <v>83.8</v>
+        <v>84</v>
       </c>
       <c r="R12">
-        <v>61.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="S12">
-        <v>100</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="T12">
         <v>100</v>
@@ -4260,7 +4251,7 @@
         <v>100</v>
       </c>
       <c r="V12">
-        <v>63.3</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -4310,13 +4301,13 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q13">
-        <v>94.59999999999999</v>
+        <v>96</v>
       </c>
       <c r="R13">
-        <v>93.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -4378,13 +4369,13 @@
         <v>75</v>
       </c>
       <c r="P14">
-        <v>95.7</v>
+        <v>97</v>
       </c>
       <c r="Q14">
-        <v>91.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="R14">
-        <v>91.5</v>
+        <v>91.3</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -4396,7 +4387,7 @@
         <v>100</v>
       </c>
       <c r="V14">
-        <v>75</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -4446,13 +4437,13 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q15">
-        <v>94.59999999999999</v>
+        <v>96</v>
       </c>
       <c r="R15">
-        <v>95.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -4514,13 +4505,13 @@
         <v>75</v>
       </c>
       <c r="P16">
-        <v>93.5</v>
+        <v>95.5</v>
       </c>
       <c r="Q16">
-        <v>91.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="R16">
-        <v>78.7</v>
+        <v>85.5</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -4532,7 +4523,7 @@
         <v>100</v>
       </c>
       <c r="V16">
-        <v>75</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -4588,7 +4579,7 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>97.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -4656,7 +4647,7 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>97.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -4718,16 +4709,16 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>93.5</v>
+        <v>94</v>
       </c>
       <c r="Q19">
-        <v>86.5</v>
+        <v>86</v>
       </c>
       <c r="R19">
-        <v>80.90000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="S19">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="T19">
         <v>100</v>
@@ -4736,7 +4727,7 @@
         <v>100</v>
       </c>
       <c r="V19">
-        <v>100</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -4854,16 +4845,16 @@
         <v>83.3</v>
       </c>
       <c r="P21">
-        <v>93.5</v>
+        <v>94</v>
       </c>
       <c r="Q21">
-        <v>83.8</v>
+        <v>84</v>
       </c>
       <c r="R21">
-        <v>89.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="T21">
         <v>100</v>
@@ -4922,10 +4913,10 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>95.7</v>
+        <v>97</v>
       </c>
       <c r="Q22">
-        <v>94.59999999999999</v>
+        <v>96</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -4990,10 +4981,10 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q23">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -5061,10 +5052,10 @@
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R24">
-        <v>89.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -5129,10 +5120,10 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>94.59999999999999</v>
+        <v>94</v>
       </c>
       <c r="R25">
-        <v>97.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -5194,16 +5185,16 @@
         <v>50</v>
       </c>
       <c r="P26">
-        <v>82.59999999999999</v>
+        <v>56.7</v>
       </c>
       <c r="Q26">
-        <v>83.8</v>
+        <v>84</v>
       </c>
       <c r="R26">
-        <v>74.5</v>
+        <v>50.7</v>
       </c>
       <c r="S26">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="T26">
         <v>100</v>
@@ -5212,7 +5203,7 @@
         <v>100</v>
       </c>
       <c r="V26">
-        <v>50</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -5262,16 +5253,16 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="Q27">
-        <v>94.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="R27">
-        <v>97.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T27">
         <v>100</v>
@@ -5330,16 +5321,16 @@
         <v>66.7</v>
       </c>
       <c r="P28">
-        <v>93.5</v>
+        <v>92.5</v>
       </c>
       <c r="Q28">
-        <v>83.8</v>
+        <v>84</v>
       </c>
       <c r="R28">
-        <v>76.59999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="S28">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="T28">
         <v>100</v>
@@ -5348,7 +5339,7 @@
         <v>100</v>
       </c>
       <c r="V28">
-        <v>66.7</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -5398,13 +5389,13 @@
         <v>75</v>
       </c>
       <c r="P29">
-        <v>93.5</v>
+        <v>94</v>
       </c>
       <c r="Q29">
-        <v>97.3</v>
+        <v>96</v>
       </c>
       <c r="R29">
-        <v>87.2</v>
+        <v>91.3</v>
       </c>
       <c r="S29">
         <v>62.5</v>
@@ -5416,7 +5407,7 @@
         <v>100</v>
       </c>
       <c r="V29">
-        <v>75</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -5469,10 +5460,10 @@
         <v>100</v>
       </c>
       <c r="Q30">
-        <v>97.3</v>
+        <v>96</v>
       </c>
       <c r="R30">
-        <v>89.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -5540,7 +5531,7 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>91.5</v>
+        <v>94.2</v>
       </c>
       <c r="S31">
         <v>100</v>
@@ -5605,10 +5596,10 @@
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>91.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="R32">
-        <v>89.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="S32">
         <v>100</v>
@@ -5670,13 +5661,13 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q33">
-        <v>86.5</v>
+        <v>88</v>
       </c>
       <c r="R33">
-        <v>95.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -5688,7 +5679,7 @@
         <v>100</v>
       </c>
       <c r="V33">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -5738,16 +5729,16 @@
         <v>100</v>
       </c>
       <c r="P34">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q34">
-        <v>94.59999999999999</v>
+        <v>94</v>
       </c>
       <c r="R34">
-        <v>48.9</v>
+        <v>65.2</v>
       </c>
       <c r="S34">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="T34">
         <v>100</v>
@@ -5813,7 +5804,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
@@ -5822,16 +5813,16 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F2" s="2">
-        <v>54.8</v>
+        <v>64.5</v>
       </c>
       <c r="G2" s="2">
-        <v>45.2</v>
+        <v>35.5</v>
       </c>
       <c r="H2">
         <v>6.6</v>
@@ -5845,7 +5836,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -5866,7 +5857,7 @@
         <v>29</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5877,7 +5868,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -5886,19 +5877,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" s="2">
-        <v>71</v>
+        <v>74.2</v>
       </c>
       <c r="G4" s="2">
-        <v>29</v>
+        <v>25.8</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5909,28 +5900,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C5">
         <v>31</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2">
-        <v>71</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>29</v>
+        <v>19.4</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5941,28 +5932,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C6">
         <v>31</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2">
-        <v>80.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>19.4</v>
+        <v>16.1</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5973,28 +5964,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7">
         <v>31</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>80.59999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="G7" s="2">
-        <v>19.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6005,7 +5996,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>61</v>
@@ -6014,19 +6005,19 @@
         <v>31</v>
       </c>
       <c r="D8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>87.09999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="G8" s="2">
-        <v>12.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H8">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6108,19 +6099,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920235</v>
+        <v>22330051920231</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>56</v>
@@ -6131,22 +6122,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920235</v>
+        <v>22330051920231</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6154,22 +6145,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920257</v>
+        <v>22330051920233</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6177,22 +6168,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920257</v>
+        <v>22330051920233</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6200,22 +6191,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920230</v>
+        <v>22330051920235</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6223,22 +6214,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920253</v>
+        <v>22330051920235</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6246,19 +6237,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920401</v>
+        <v>22330051920230</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
         <v>56</v>
@@ -6272,19 +6263,19 @@
         <v>22330051920259</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G9">
         <v>5</v>

--- a/grupos/4ALCV - Estadisticos 20232.xlsx
+++ b/grupos/4ALCV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="87">
   <si>
     <t>Materia</t>
   </si>
@@ -191,15 +191,15 @@
     <t>González Nuñez Veronica</t>
   </si>
   <si>
+    <t>Valerio González Valeria</t>
+  </si>
+  <si>
+    <t>Reyes Cruz Eder Yaveth</t>
+  </si>
+  <si>
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
-    <t>Valerio González Valeria</t>
-  </si>
-  <si>
-    <t>Reyes Cruz Eder Yaveth</t>
-  </si>
-  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
@@ -218,46 +218,64 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>LLANOS</t>
+  </si>
+  <si>
+    <t>DE ROMAN</t>
+  </si>
+  <si>
     <t>ARELLANO</t>
   </si>
   <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
     <t>BONILLA</t>
   </si>
   <si>
-    <t>DE ROMAN</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
     <t>FIERROS</t>
   </si>
   <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
     <t>IBAÑEZ</t>
   </si>
   <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
     <t>TZOMPAXTLE</t>
   </si>
   <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>SERGIO</t>
+  </si>
+  <si>
+    <t>NATHALI</t>
+  </si>
+  <si>
     <t>ALDO EMANUEL</t>
   </si>
   <si>
+    <t>AZURA</t>
+  </si>
+  <si>
     <t>FERNANDA MARGARITA</t>
-  </si>
-  <si>
-    <t>NATHALI</t>
-  </si>
-  <si>
-    <t>AZURA</t>
   </si>
   <si>
     <t>BRENDA JANELY</t>
@@ -820,10 +838,10 @@
         <v>5</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>9</v>
@@ -909,10 +927,10 @@
         <v>8</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -930,7 +948,7 @@
         <v>8</v>
       </c>
       <c r="AA5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB5">
         <v>10</v>
@@ -998,10 +1016,10 @@
         <v>8</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
         <v>10</v>
@@ -1087,10 +1105,10 @@
         <v>5</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -1108,7 +1126,7 @@
         <v>5</v>
       </c>
       <c r="AA7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB7">
         <v>7</v>
@@ -1176,10 +1194,10 @@
         <v>5</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1265,10 +1283,10 @@
         <v>5</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>6</v>
@@ -1286,10 +1304,10 @@
         <v>5</v>
       </c>
       <c r="AA9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC9">
         <v>7</v>
@@ -1354,10 +1372,10 @@
         <v>5</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
         <v>9</v>
@@ -1375,7 +1393,7 @@
         <v>7</v>
       </c>
       <c r="AA10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB10">
         <v>10</v>
@@ -1443,10 +1461,10 @@
         <v>5</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V11">
         <v>5</v>
@@ -1467,7 +1485,7 @@
         <v>5</v>
       </c>
       <c r="AB11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC11">
         <v>7</v>
@@ -1532,10 +1550,10 @@
         <v>5</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -1556,7 +1574,7 @@
         <v>7</v>
       </c>
       <c r="AB12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC12">
         <v>5</v>
@@ -1621,10 +1639,10 @@
         <v>5</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
         <v>10</v>
@@ -1710,10 +1728,10 @@
         <v>6</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
         <v>9</v>
@@ -1799,10 +1817,10 @@
         <v>7</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
         <v>10</v>
@@ -1888,10 +1906,10 @@
         <v>5</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -1909,7 +1927,7 @@
         <v>5</v>
       </c>
       <c r="AA16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB16">
         <v>6</v>
@@ -1977,10 +1995,10 @@
         <v>8</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
         <v>10</v>
@@ -2066,10 +2084,10 @@
         <v>8</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
         <v>10</v>
@@ -2155,10 +2173,10 @@
         <v>5</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -2176,10 +2194,10 @@
         <v>5</v>
       </c>
       <c r="AA19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC19">
         <v>7</v>
@@ -2244,10 +2262,10 @@
         <v>7</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
         <v>10</v>
@@ -2333,10 +2351,10 @@
         <v>5</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -2354,7 +2372,7 @@
         <v>5</v>
       </c>
       <c r="AA21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB21">
         <v>6</v>
@@ -2422,10 +2440,10 @@
         <v>5</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>10</v>
@@ -2511,10 +2529,10 @@
         <v>5</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
         <v>10</v>
@@ -2535,7 +2553,7 @@
         <v>8</v>
       </c>
       <c r="AB23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC23">
         <v>9</v>
@@ -2600,10 +2618,10 @@
         <v>5</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
         <v>10</v>
@@ -2689,10 +2707,10 @@
         <v>7</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>10</v>
@@ -2778,10 +2796,10 @@
         <v>5</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V26">
         <v>5</v>
@@ -2867,10 +2885,10 @@
         <v>5</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>10</v>
@@ -2956,10 +2974,10 @@
         <v>6</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V28">
         <v>8</v>
@@ -2977,7 +2995,7 @@
         <v>5</v>
       </c>
       <c r="AA28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB28">
         <v>7</v>
@@ -3045,10 +3063,10 @@
         <v>5</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V29">
         <v>6</v>
@@ -3134,10 +3152,10 @@
         <v>7</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
         <v>10</v>
@@ -3223,10 +3241,10 @@
         <v>5</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
         <v>10</v>
@@ -3312,10 +3330,10 @@
         <v>7</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
         <v>10</v>
@@ -3333,7 +3351,7 @@
         <v>6</v>
       </c>
       <c r="AA32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB32">
         <v>9</v>
@@ -3401,10 +3419,10 @@
         <v>5</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
         <v>8</v>
@@ -3490,10 +3508,10 @@
         <v>5</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V34">
         <v>10</v>
@@ -5836,7 +5854,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -5845,19 +5863,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2">
-        <v>71</v>
+        <v>74.2</v>
       </c>
       <c r="G3" s="2">
-        <v>29</v>
+        <v>25.8</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5868,7 +5886,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -5877,19 +5895,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>74.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>25.8</v>
+        <v>16.1</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5900,28 +5918,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C5">
         <v>31</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>80.59999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>19.4</v>
+        <v>12.9</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5932,28 +5950,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C6">
         <v>31</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>83.90000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="G6" s="2">
-        <v>16.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5964,10 +5982,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7">
         <v>31</v>
@@ -5985,7 +6003,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5996,10 +6014,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C8">
         <v>31</v>
@@ -6017,7 +6035,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="H8">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6067,7 +6085,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6099,22 +6117,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920231</v>
+        <v>22330051920369</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6122,22 +6140,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920231</v>
+        <v>22330051920369</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6145,22 +6163,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920233</v>
+        <v>21330051420317</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6168,22 +6186,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920233</v>
+        <v>21330051420317</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6197,10 +6215,10 @@
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -6220,16 +6238,16 @@
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6237,16 +6255,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920230</v>
+        <v>22330051920231</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -6260,24 +6278,70 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920259</v>
+        <v>22330051920230</v>
       </c>
       <c r="B9" t="s">
         <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920233</v>
+      </c>
+      <c r="B10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920259</v>
+      </c>
+      <c r="B11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11">
         <v>5</v>
       </c>
     </row>
